--- a/docs/tampermonkey/发票模板/佰通清关发票模板.xlsx
+++ b/docs/tampermonkey/发票模板/佰通清关发票模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\代码\hth123321\docs\tampermonkey\发票模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D12ACF-5667-4E22-B560-7C4AE87640B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A65B2C-4F74-492A-ADA9-150B694D4F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,7 +394,7 @@
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>{{t.product..brand_name}}</t>
+    <t>{{t.brand}}</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
 </sst>
